--- a/Data/EXCEL/Transfer/salemon/20240711/4544-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/4544-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57698EAF-0DCC-4541-9933-5682096AC267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B2D9CB-FAC4-4048-95AD-3792FD79227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{81591C98-954E-4781-9D98-095BE6331E18}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{DD6DC054-2E36-4D4B-8DC5-A35A726BD616}"/>
   </bookViews>
   <sheets>
     <sheet name="4544-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,21 +1261,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C014D7-24D5-4E05-A60C-6EB28333AF59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A5961E-D605-41EF-A4F4-841C7F21DC28}">
   <dimension ref="A1:Q294"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>-2.27</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>-7.73</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>-5.93</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>-2.29</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>-4.25</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>-4.93</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>-4.8099999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>-9.99</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>-13.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>-18.899999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>-8.42</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>-18.2</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>-30.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>-9.19</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>-22.7</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>-24.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>-24.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>-25.4</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>-26</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>-23.3</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>-5.71</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>-25.6</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>-1.87</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>-9.83</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>-25.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>-3.68</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>-6.08</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>-9.59</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>-9.34</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>-16.100000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>-35.4</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>-23.2</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>-13.7</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>-6.54</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41699</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>-13.7</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41640</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>-18.399999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41579</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>-19.899999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8260,7 +8260,7 @@
         <v>-20.3</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>41518</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>-21.6</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>41456</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>-20.5</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>41395</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>-28.3</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>-24.4</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>41334</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>41275</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>41214</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8896,747 +8896,747 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>41699</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>41640</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="10">
         <v>41579</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="10">
         <v>41518</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>41456</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>41395</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>41334</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="10">
         <v>41275</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="10">
         <v>41214</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>41183</v>
       </c>
